--- a/data/trans_camb/P12_3_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P12_3_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,99</t>
+          <t>2,03; 7,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,44</t>
+          <t>3,09; 8,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,22</t>
+          <t>3,08; 8,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,39</t>
+          <t>5,13; 11,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 11,17</t>
+          <t>5,17; 11,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,04</t>
+          <t>4,12; 9,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,5</t>
+          <t>4,39; 8,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,06</t>
+          <t>4,71; 9,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 8,02</t>
+          <t>4,25; 7,99</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,78; 233,87</t>
+          <t>36,6; 241,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,0; 281,65</t>
+          <t>57,99; 274,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58,88; 275,05</t>
+          <t>60,26; 284,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72,71; 246,54</t>
+          <t>69,56; 269,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,79; 247,05</t>
+          <t>68,16; 251,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,19; 217,11</t>
+          <t>50,73; 212,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,45; 207,23</t>
+          <t>78,08; 211,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,71; 227,65</t>
+          <t>82,67; 224,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76,56; 195,84</t>
+          <t>74,32; 201,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,51</t>
+          <t>-0,22; 4,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,87</t>
+          <t>-2,56; 1,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 5,29</t>
+          <t>-2,39; 5,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,84</t>
+          <t>2,3; 8,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,15</t>
+          <t>-2,23; 3,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,98</t>
+          <t>3,45; 9,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,47</t>
+          <t>1,47; 5,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,74</t>
+          <t>-1,64; 1,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 6,17</t>
+          <t>0,21; 6,07</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 91,42</t>
+          <t>-3,2; 88,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 38,1</t>
+          <t>-35,65; 35,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 100,33</t>
+          <t>-34,89; 100,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,62; 103,87</t>
+          <t>22,61; 108,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 44,04</t>
+          <t>-22,5; 41,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,61; 120,98</t>
+          <t>33,7; 122,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,92; 80,85</t>
+          <t>16,99; 79,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 25,8</t>
+          <t>-20,32; 26,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 91,62</t>
+          <t>3,5; 90,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,54</t>
+          <t>-0,84; 4,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,35</t>
+          <t>-0,8; 4,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,5</t>
+          <t>2,91; 9,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 6,99</t>
+          <t>0,86; 6,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,26</t>
+          <t>0,24; 6,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 5,46</t>
+          <t>-4,01; 5,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,85</t>
+          <t>0,74; 4,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,5</t>
+          <t>0,52; 4,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 6,02</t>
+          <t>-0,28; 6,1</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 116,32</t>
+          <t>-14,44; 113,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 107,25</t>
+          <t>-12,39; 116,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,11; 238,52</t>
+          <t>42,24; 243,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 109,58</t>
+          <t>8,79; 108,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 101,38</t>
+          <t>2,64; 102,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 79,48</t>
+          <t>-42,91; 74,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,29; 88,52</t>
+          <t>9,75; 89,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,21; 85,17</t>
+          <t>7,16; 81,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 104,89</t>
+          <t>-2,05; 108,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,2</t>
+          <t>1,41; 6,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,59</t>
+          <t>0,85; 5,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,03</t>
+          <t>3,88; 9,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,34</t>
+          <t>0,4; 6,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 5,86</t>
+          <t>0,02; 5,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,36</t>
+          <t>1,1; 7,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,39</t>
+          <t>1,6; 5,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,85</t>
+          <t>1,35; 5,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,64</t>
+          <t>3,51; 7,69</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,12; 151,02</t>
+          <t>22,04; 156,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,82; 135,26</t>
+          <t>12,23; 136,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69,3; 222,75</t>
+          <t>60,95; 226,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,91; 68,62</t>
+          <t>2,55; 64,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 61,9</t>
+          <t>-1,34; 61,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,43; 79,03</t>
+          <t>9,56; 80,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,29; 74,61</t>
+          <t>18,94; 77,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,79; 69,02</t>
+          <t>14,49; 71,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42,95; 111,42</t>
+          <t>39,9; 108,43</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,26</t>
+          <t>1,86; 4,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,55</t>
+          <t>1,15; 3,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,39</t>
+          <t>2,45; 6,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,41</t>
+          <t>3,32; 6,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,58</t>
+          <t>1,8; 4,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,31</t>
+          <t>2,07; 6,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,97</t>
+          <t>2,96; 4,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,79</t>
+          <t>1,87; 3,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,91</t>
+          <t>3,07; 5,88</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>31,11; 95,5</t>
+          <t>32,08; 92,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>18,88; 76,73</t>
+          <t>20,74; 77,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47,95; 140,92</t>
+          <t>47,55; 137,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36,74; 81,02</t>
+          <t>36,02; 80,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>18,78; 59,04</t>
+          <t>19,76; 61,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,59; 81,16</t>
+          <t>24,13; 80,3</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,3; 80,8</t>
+          <t>40,17; 78,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26,8; 59,55</t>
+          <t>26,48; 61,25</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>45,97; 91,81</t>
+          <t>44,83; 91,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_3_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P12_3_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>5,91</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,55</t>
+          <t>6,72</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,16</t>
+          <t>6,35</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,04</t>
+          <t>1,94; 7,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,33</t>
+          <t>2,94; 8,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,53</t>
+          <t>3,17; 8,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 11,56</t>
+          <t>4,92; 11,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 11,72</t>
+          <t>5,21; 11,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,27</t>
+          <t>4,31; 9,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,39</t>
+          <t>4,33; 8,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 9,07</t>
+          <t>4,56; 8,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 7,99</t>
+          <t>4,36; 8,18</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143,02%</t>
+          <t>148,81%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>114,91%</t>
+          <t>117,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>127,44%</t>
+          <t>131,46%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,6; 241,22</t>
+          <t>40,07; 228,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,99; 274,86</t>
+          <t>58,55; 279,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60,26; 284,21</t>
+          <t>62,67; 284,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69,56; 269,07</t>
+          <t>68,61; 251,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,16; 251,66</t>
+          <t>74,71; 249,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,73; 212,2</t>
+          <t>59,4; 222,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,08; 211,75</t>
+          <t>74,22; 201,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>82,67; 224,05</t>
+          <t>79,07; 214,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,32; 201,52</t>
+          <t>73,71; 197,91</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>3,21</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>6,55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,75</t>
+          <t>4,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,42</t>
+          <t>-0,22; 4,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,72</t>
+          <t>-2,77; 1,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 5,49</t>
+          <t>0,81; 5,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 8,18</t>
+          <t>1,68; 8,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,06</t>
+          <t>-2,33; 3,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,26</t>
+          <t>3,89; 9,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,28</t>
+          <t>1,7; 5,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,73</t>
+          <t>-1,63; 1,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 6,07</t>
+          <t>3,09; 6,72</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 88,86</t>
+          <t>-3,12; 92,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,65; 35,9</t>
+          <t>-39,25; 33,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 100,33</t>
+          <t>10,79; 115,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,61; 108,97</t>
+          <t>15,76; 111,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 41,77</t>
+          <t>-23,2; 43,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,7; 122,87</t>
+          <t>36,08; 128,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,99; 79,0</t>
+          <t>20,11; 81,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 26,93</t>
+          <t>-19,65; 27,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 90,67</t>
+          <t>36,52; 104,35</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,83</t>
+          <t>5,72</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>5,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,32</t>
+          <t>-0,87; 4,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,51</t>
+          <t>-0,89; 4,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 9,45</t>
+          <t>2,95; 8,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 6,82</t>
+          <t>0,82; 6,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 6,16</t>
+          <t>0,26; 6,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 5,03</t>
+          <t>1,79; 7,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,86</t>
+          <t>0,79; 4,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,54</t>
+          <t>0,57; 4,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 6,1</t>
+          <t>3,15; 7,57</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114,92%</t>
+          <t>112,86%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 113,78</t>
+          <t>-15,32; 109,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 116,66</t>
+          <t>-14,05; 107,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,24; 243,28</t>
+          <t>41,42; 222,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,79; 108,09</t>
+          <t>7,97; 109,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 102,27</t>
+          <t>0,12; 98,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,91; 74,35</t>
+          <t>17,5; 125,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,75; 89,04</t>
+          <t>9,97; 92,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,16; 81,68</t>
+          <t>6,92; 90,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 108,71</t>
+          <t>42,53; 144,6</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>7,3</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,58</t>
+          <t>6,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,56</t>
+          <t>6,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,3</t>
+          <t>1,55; 6,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,56</t>
+          <t>0,93; 5,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 9,0</t>
+          <t>4,68; 10,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 6,17</t>
+          <t>0,2; 6,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,81</t>
+          <t>-0,07; 6,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,67</t>
+          <t>3,47; 8,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,42</t>
+          <t>1,63; 5,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,05</t>
+          <t>1,23; 5,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,69</t>
+          <t>5,0; 8,7</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131,75%</t>
+          <t>147,71%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,04; 156,5</t>
+          <t>22,63; 156,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,23; 136,08</t>
+          <t>16,93; 138,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60,95; 226,32</t>
+          <t>73,49; 255,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 64,99</t>
+          <t>1,23; 67,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 61,75</t>
+          <t>-0,7; 67,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,56; 80,87</t>
+          <t>29,32; 94,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,94; 77,67</t>
+          <t>17,67; 74,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,49; 71,51</t>
+          <t>13,08; 72,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39,9; 108,43</t>
+          <t>56,27; 123,19</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>5,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,32</t>
+          <t>1,77; 4,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,59</t>
+          <t>1,15; 3,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,3</t>
+          <t>4,12; 6,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,28</t>
+          <t>3,32; 6,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,79</t>
+          <t>1,77; 4,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,22</t>
+          <t>4,76; 7,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,94</t>
+          <t>2,96; 4,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,79</t>
+          <t>1,85; 3,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,88</t>
+          <t>4,91; 6,82</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>108,11%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>32,08; 92,47</t>
+          <t>30,93; 94,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20,74; 77,12</t>
+          <t>21,24; 80,27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47,55; 137,08</t>
+          <t>73,28; 157,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36,02; 80,83</t>
+          <t>35,59; 83,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>19,76; 61,45</t>
+          <t>18,96; 60,66</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,13; 80,3</t>
+          <t>51,69; 99,98</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,17; 78,25</t>
+          <t>40,59; 75,44</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26,48; 61,25</t>
+          <t>24,64; 58,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>44,83; 91,64</t>
+          <t>67,6; 107,19</t>
         </is>
       </c>
     </row>
